--- a/artfynd/A 44892-2021 artfynd.xlsx
+++ b/artfynd/A 44892-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44892-2021 artfynd.xlsx
+++ b/artfynd/A 44892-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2080,14 +2080,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>54131972</v>
+        <v>106228630</v>
       </c>
       <c r="B14" t="n">
-        <v>96239</v>
+        <v>78596</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2096,52 +2096,44 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>504</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ö Holmtjärnmyran, Vb</t>
+          <t>Nordost Stor-Mullbergsmyran, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>755932.8622654119</v>
+        <v>755328.5477977782</v>
       </c>
       <c r="R14" t="n">
-        <v>7212956.944681674</v>
+        <v>7212410.526480958</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2165,7 +2157,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
+          <t>2019-08-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2175,7 +2167,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
+          <t>2019-08-28</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2189,28 +2181,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Henrik Sporrong</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Henrik Sporrong</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>54138124</v>
+        <v>106228626</v>
       </c>
       <c r="B15" t="n">
-        <v>96239</v>
+        <v>78569</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2219,52 +2212,48 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Slänt Nybäck 1:4, Vb</t>
+          <t>Nordost Stor-Mullbergsmyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>756100.0067520952</v>
+        <v>755328.5477977782</v>
       </c>
       <c r="R15" t="n">
-        <v>7213229.846257342</v>
+        <v>7212410.526480958</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2288,7 +2277,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
+          <t>2019-08-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2298,7 +2287,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
+          <t>2019-08-28</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2312,261 +2301,22 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Henrik Sporrong</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Henrik Sporrong</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>106228630</v>
-      </c>
-      <c r="B16" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Nordost Stor-Mullbergsmyran, Vb</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>755328.5477977782</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7212410.526480958</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Jörn</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2019-08-28</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2019-08-28</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>106228626</v>
-      </c>
-      <c r="B17" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Nordost Stor-Mullbergsmyran, Vb</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>755328.5477977782</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7212410.526480958</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Jörn</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2019-08-28</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2019-08-28</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
